--- a/album_List.xlsx
+++ b/album_List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\675939\Documents\PRIVATE\SensuCarens\website_sozai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaki/Documents/SensuCarens/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26D7C50B-5D1D-47A0-82C4-43F227377D49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EC5126-168E-E344-8D3A-6CEC93D86468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="940" windowWidth="14400" windowHeight="8170" xr2:uid="{D3B93528-F99F-4BFB-A2BD-12862A952DCF}"/>
+    <workbookView xWindow="820" yWindow="940" windowWidth="22960" windowHeight="8180" xr2:uid="{D3B93528-F99F-4BFB-A2BD-12862A952DCF}"/>
   </bookViews>
   <sheets>
     <sheet name="アルバムリスト" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
   <si>
     <t>ambiguous</t>
     <phoneticPr fontId="1"/>
@@ -139,6 +139,10 @@
   </si>
   <si>
     <t>アルバムタイトル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>artwork:Shinichi Wade</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -146,7 +150,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -523,10 +527,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{837167A9-38F9-42F6-B0AE-D19E562E9CED}">
-  <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -546,7 +550,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -565,8 +569,11 @@
       <c r="F2" t="s">
         <v>0</v>
       </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:7">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -582,8 +589,11 @@
       <c r="E3" t="s">
         <v>11</v>
       </c>
+      <c r="G3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>12</v>
       </c>
